--- a/menu.xlsx
+++ b/menu.xlsx
@@ -1,20 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DATA\01. RELIABILITY PROJECT\DATABASE PROJECT\SATSUN Coffee\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9222C353-C521-417B-8667-CC373C4ED852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Kategori</t>
   </si>
@@ -27,60 +38,12 @@
   <si>
     <t>Gambar</t>
   </si>
-  <si>
-    <t>Coffee</t>
-  </si>
-  <si>
-    <t>Non-Coffee</t>
-  </si>
-  <si>
-    <t>Snack</t>
-  </si>
-  <si>
-    <t>Dessert</t>
-  </si>
-  <si>
-    <t>Satsun Signature Latte</t>
-  </si>
-  <si>
-    <t>Espresso</t>
-  </si>
-  <si>
-    <t>Matcha Latte</t>
-  </si>
-  <si>
-    <t>Croissant Butter</t>
-  </si>
-  <si>
-    <t>Satsun Americano Robusta</t>
-  </si>
-  <si>
-    <t>Lotus cheese Cake</t>
-  </si>
-  <si>
-    <t>satsun_signature_latte.jpg</t>
-  </si>
-  <si>
-    <t>espresso.jpg</t>
-  </si>
-  <si>
-    <t>matcha_latte.jpg</t>
-  </si>
-  <si>
-    <t>croissant_butter.jpg</t>
-  </si>
-  <si>
-    <t>satsun_americano_robusta.jpg</t>
-  </si>
-  <si>
-    <t>lotus_cheese_cake.jpg</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,13 +106,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -187,7 +158,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -221,6 +192,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -255,9 +227,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -430,11 +403,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -448,90 +426,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2">
-        <v>28000</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>18000</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4">
-        <v>25000</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>22000</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6">
-        <v>21000</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>35000</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DATA\01. RELIABILITY PROJECT\DATABASE PROJECT\SATSUN Coffee\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9222C353-C521-417B-8667-CC373C4ED852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B1FEC4-B9B6-4297-91EA-111061B1BA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>Kategori</t>
   </si>
@@ -37,6 +37,21 @@
   </si>
   <si>
     <t>Gambar</t>
+  </si>
+  <si>
+    <t>Coffee</t>
+  </si>
+  <si>
+    <t>Matcha Latte</t>
+  </si>
+  <si>
+    <t>Main Menu</t>
+  </si>
+  <si>
+    <t>Sate Thaican</t>
+  </si>
+  <si>
+    <t>Ikan Bakar Kakap Merah - 8 ons</t>
   </si>
 </sst>
 </file>
@@ -404,11 +419,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -426,6 +441,39 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>70000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
